--- a/output/laminas_comunales/comunal_o_ocup_a_2019_o_higgins.xlsx
+++ b/output/laminas_comunales/comunal_o_ocup_a_2019_o_higgins.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C225"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -375,46 +375,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>6116</t>
+          <t>6108</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Requínoa</t>
+          <t>Machalí</t>
         </is>
       </c>
       <c r="C2">
-        <v>46.7536811828613</v>
+        <v>64.7937850952148</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6102</t>
+          <t>6116</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Codegua</t>
+          <t>Requínoa</t>
         </is>
       </c>
       <c r="C3">
-        <v>44.1166076660156</v>
+        <v>64.6711959838867</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6108</t>
+          <t>6112</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Machalí</t>
+          <t>Peumo</t>
         </is>
       </c>
       <c r="C4">
-        <v>43.8267402648926</v>
+        <v>64.1533966064453</v>
       </c>
     </row>
     <row r="5">
@@ -429,82 +429,82 @@
         </is>
       </c>
       <c r="C5">
-        <v>43.7957000732422</v>
+        <v>62.0682792663574</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6112</t>
+          <t>6101</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Peumo</t>
+          <t>Rancagua</t>
         </is>
       </c>
       <c r="C6">
-        <v>42.8188247680664</v>
+        <v>61.9186668395996</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6101</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rancagua</t>
+          <t>San Fernando</t>
         </is>
       </c>
       <c r="C7">
-        <v>42.3630447387695</v>
+        <v>61.8789138793945</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>6111</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>San Fernando</t>
+          <t>Olivar</t>
         </is>
       </c>
       <c r="C8">
-        <v>42.0023460388184</v>
+        <v>61.3280792236328</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6111</t>
+          <t>6102</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Olivar</t>
+          <t>Codegua</t>
         </is>
       </c>
       <c r="C9">
-        <v>41.3619804382324</v>
+        <v>60.724925994873</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6115</t>
+          <t>6105</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rengo</t>
+          <t>Doñihue</t>
         </is>
       </c>
       <c r="C10">
-        <v>41.1829833984375</v>
+        <v>60.6501159667969</v>
       </c>
     </row>
     <row r="11">
@@ -519,337 +519,3217 @@
         </is>
       </c>
       <c r="C11">
-        <v>40.5192451477051</v>
+        <v>60.1661796569824</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6110</t>
+          <t>6115</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mostazal</t>
+          <t>Rengo</t>
         </is>
       </c>
       <c r="C12">
-        <v>40.4676094055176</v>
+        <v>60.0973243713379</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6104</t>
+          <t>6107</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Coltauco</t>
+          <t>Las Cabras</t>
         </is>
       </c>
       <c r="C13">
-        <v>40.2159461975098</v>
+        <v>59.4035377502441</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6105</t>
+          <t>6307</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Doñihue</t>
+          <t>Peralillo</t>
         </is>
       </c>
       <c r="C14">
-        <v>40.2057151794434</v>
+        <v>59.2809677124023</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6107</t>
+          <t>6104</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Las Cabras</t>
+          <t>Coltauco</t>
         </is>
       </c>
       <c r="C15">
-        <v>40.0678215026855</v>
+        <v>58.8949089050293</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6303</t>
+          <t>6117</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Chimbarongo</t>
+          <t>San Vicente</t>
         </is>
       </c>
       <c r="C16">
-        <v>39.8122787475586</v>
+        <v>58.6315879821777</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6308</t>
+          <t>6303</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Placilla</t>
+          <t>Chimbarongo</t>
         </is>
       </c>
       <c r="C17">
-        <v>39.1652450561523</v>
+        <v>58.3806304931641</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6307</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Peralillo</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="C18">
-        <v>38.5677146911621</v>
+        <v>57.8239479064941</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6310</t>
+          <t>6110</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Mostazal</t>
         </is>
       </c>
       <c r="C19">
-        <v>38.5662117004395</v>
+        <v>57.8007507324219</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6305</t>
+          <t>6308</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nancagua</t>
+          <t>Placilla</t>
         </is>
       </c>
       <c r="C20">
-        <v>37.791187286377</v>
+        <v>57.3438873291016</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6113</t>
+          <t>6116</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pichidegua</t>
+          <t>Requínoa</t>
         </is>
       </c>
       <c r="C21">
-        <v>37.4720153808594</v>
+        <v>57.2144622802734</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6117</t>
+          <t>6113</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>San Vicente</t>
+          <t>Pichidegua</t>
         </is>
       </c>
       <c r="C22">
-        <v>37.4311637878418</v>
+        <v>56.8768157958984</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6109</t>
+          <t>6305</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Malloa</t>
+          <t>Nancagua</t>
         </is>
       </c>
       <c r="C23">
-        <v>36.4101257324219</v>
+        <v>56.8122825622559</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6114</t>
+          <t>6116</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Quinta de Tilcoco</t>
+          <t>Requínoa</t>
         </is>
       </c>
       <c r="C24">
-        <v>35.2351837158203</v>
+        <v>56.629280090332</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6302</t>
+          <t>6106</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Chépica</t>
+          <t>Graneros</t>
         </is>
       </c>
       <c r="C25">
-        <v>34.4812889099121</v>
+        <v>55.475944519043</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>6304</t>
+          <t>6102</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Lolol</t>
+          <t>Codegua</t>
         </is>
       </c>
       <c r="C26">
-        <v>32.9157371520996</v>
+        <v>55.4537086486816</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>6103</t>
+          <t>6108</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Coinco</t>
+          <t>Machalí</t>
         </is>
       </c>
       <c r="C27">
-        <v>32.2751312255859</v>
+        <v>54.9695587158203</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>6203</t>
+          <t>6108</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Litueche</t>
+          <t>Machalí</t>
         </is>
       </c>
       <c r="C28">
-        <v>31.9640998840332</v>
+        <v>54.8326225280762</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>6202</t>
+          <t>6112</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>La Estrella</t>
+          <t>Peumo</t>
         </is>
       </c>
       <c r="C29">
-        <v>31.7925586700439</v>
+        <v>54.327335357666</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>6201</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Pichilemu</t>
+          <t>San Fernando</t>
         </is>
       </c>
       <c r="C30">
-        <v>31.6741790771484</v>
+        <v>54.2780303955078</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6309</t>
+          <t>6114</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Pumanque</t>
+          <t>Quinta de Tilcoco</t>
         </is>
       </c>
       <c r="C31">
-        <v>31.4295253753662</v>
+        <v>54.1362342834473</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>6206</t>
+          <t>6102</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Paredones</t>
+          <t>Codegua</t>
         </is>
       </c>
       <c r="C32">
-        <v>28.4197483062744</v>
+        <v>54.1020088195801</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>6109</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Malloa</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>53.8910636901855</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>6304</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Lolol</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>53.6469879150391</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>6101</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Rancagua</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>53.5513725280762</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>6106</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Graneros</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>53.2657585144043</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>6112</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Peumo</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>52.666934967041</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>6202</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>La Estrella</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>52.4467468261719</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>6302</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Chépica</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>52.4012794494629</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>6309</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Pumanque</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>52.1326446533203</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>6115</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Rengo</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>51.9355773925781</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>6111</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Olivar</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>51.5281295776367</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>6101</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Rancagua</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>51.4329986572266</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>6111</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Olivar</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>51.1413917541504</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>6103</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Coinco</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>51.102855682373</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>6110</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Mostazal</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>51.0012855529785</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>6110</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Mostazal</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>50.8510551452637</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>6306</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Palmilla</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>50.4808311462402</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>6105</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Doñihue</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>50.0468597412109</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>6306</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Palmilla</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>49.9090156555176</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>6104</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Coltauco</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>49.9037780761719</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>6115</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Rengo</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>49.559986114502</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>6105</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Doñihue</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>49.308277130127</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>6203</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Litueche</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>49.296215057373</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>6308</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Placilla</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>49.2865905761719</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>6301</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>San Fernando</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>49.0083961486816</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>6303</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Chimbarongo</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>48.9310569763184</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>6307</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Peralillo</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>48.9038505554199</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>6107</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Las Cabras</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>48.743106842041</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>6107</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Las Cabras</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>48.7204742431641</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>6310</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Santa Cruz</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>48.5669479370117</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>6117</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>San Vicente</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>48.5587615966797</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>6104</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Coltauco</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>48.5475730895996</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>6303</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Chimbarongo</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>48.5365676879883</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>6307</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Peralillo</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>48.1682624816895</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>6308</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Placilla</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>48.0887641906738</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>6305</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Nancagua</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>47.2924957275391</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>6201</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Pichilemu</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>46.9379119873047</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>6113</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Pichidegua</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>46.8182716369629</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>6116</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Requínoa</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>46.7536811828613</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>6113</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Pichidegua</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>46.5673637390137</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>6305</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Nancagua</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>46.2162780761719</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>6205</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>Navidad</t>
         </is>
       </c>
-      <c r="C33">
+      <c r="C73">
+        <v>45.3685913085938</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>6206</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Paredones</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>44.5943946838379</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6310</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Santa Cruz</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>44.5232543945312</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>6102</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Codegua</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>44.1166076660156</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>6302</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Chépica</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>43.9461212158203</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>6117</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>San Vicente</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>43.9000701904297</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>6108</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Machalí</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>43.8267402648926</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>6106</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Graneros</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>43.7957000732422</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>6109</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Malloa</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>43.4444427490234</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>6109</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Malloa</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>43.0045547485351</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>6112</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Peumo</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>42.8188247680664</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>6202</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>La Estrella</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>42.8085517883301</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>6304</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Lolol</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>42.4703598022461</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>6101</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Rancagua</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>42.3630447387695</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>6304</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Lolol</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>42.2423629760742</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>6302</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Chépica</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>42.2210235595703</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>6103</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Coinco</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>42.1631698608398</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>6301</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>San Fernando</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>42.0023460388184</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>6116</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Requínoa</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>41.4980049133301</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>6111</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Olivar</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>41.3619804382324</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>6202</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>La Estrella</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>41.3512840270996</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>6115</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Rengo</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>41.1829833984375</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>6309</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Pumanque</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>40.9820594787598</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>6309</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Pumanque</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>40.8151664733887</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>6103</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Coinco</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>40.8069000244141</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>6306</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Palmilla</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>40.5192451477051</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>6110</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Mostazal</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>40.4676094055176</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>6114</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Quinta de Tilcoco</t>
+        </is>
+      </c>
+      <c r="C100">
+        <v>40.245189666748</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>6104</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Coltauco</t>
+        </is>
+      </c>
+      <c r="C101">
+        <v>40.2159461975098</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>6105</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Doñihue</t>
+        </is>
+      </c>
+      <c r="C102">
+        <v>40.2057151794434</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>6203</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Litueche</t>
+        </is>
+      </c>
+      <c r="C103">
+        <v>40.1552276611328</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>6107</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Las Cabras</t>
+        </is>
+      </c>
+      <c r="C104">
+        <v>40.0678215026855</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>6201</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Pichilemu</t>
+        </is>
+      </c>
+      <c r="C105">
+        <v>39.951171875</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>6303</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Chimbarongo</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>39.8122787475586</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>6104</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Coltauco</t>
+        </is>
+      </c>
+      <c r="C107">
+        <v>39.5893974304199</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>6306</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Palmilla</t>
+        </is>
+      </c>
+      <c r="C108">
+        <v>39.3106269836426</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>6114</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Quinta de Tilcoco</t>
+        </is>
+      </c>
+      <c r="C109">
+        <v>39.2833099365234</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>6308</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Placilla</t>
+        </is>
+      </c>
+      <c r="C110">
+        <v>39.1652450561523</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>6203</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Litueche</t>
+        </is>
+      </c>
+      <c r="C111">
+        <v>39.0530548095703</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>6102</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Codegua</t>
+        </is>
+      </c>
+      <c r="C112">
+        <v>39.0424346923828</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>6107</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Las Cabras</t>
+        </is>
+      </c>
+      <c r="C113">
+        <v>38.6255073547363</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>6307</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Peralillo</t>
+        </is>
+      </c>
+      <c r="C114">
+        <v>38.5677146911621</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>6310</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Santa Cruz</t>
+        </is>
+      </c>
+      <c r="C115">
+        <v>38.5662117004395</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>6112</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Peumo</t>
+        </is>
+      </c>
+      <c r="C116">
+        <v>38.3242607116699</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>6305</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Nancagua</t>
+        </is>
+      </c>
+      <c r="C117">
+        <v>37.791187286377</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>6113</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Pichidegua</t>
+        </is>
+      </c>
+      <c r="C118">
+        <v>37.4720153808594</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>6109</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Malloa</t>
+        </is>
+      </c>
+      <c r="C119">
+        <v>37.459415435791</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>6117</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>San Vicente</t>
+        </is>
+      </c>
+      <c r="C120">
+        <v>37.4311637878418</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>6308</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Placilla</t>
+        </is>
+      </c>
+      <c r="C121">
+        <v>37.3942070007324</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>6106</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Graneros</t>
+        </is>
+      </c>
+      <c r="C122">
+        <v>37.3128318786621</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>6303</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Chimbarongo</t>
+        </is>
+      </c>
+      <c r="C123">
+        <v>36.9464645385742</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>6101</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Rancagua</t>
+        </is>
+      </c>
+      <c r="C124">
+        <v>36.9103546142578</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>6115</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Rengo</t>
+        </is>
+      </c>
+      <c r="C125">
+        <v>36.5865631103516</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>6113</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Pichidegua</t>
+        </is>
+      </c>
+      <c r="C126">
+        <v>36.5160026550293</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>6109</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Malloa</t>
+        </is>
+      </c>
+      <c r="C127">
+        <v>36.4101257324219</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>6110</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Mostazal</t>
+        </is>
+      </c>
+      <c r="C128">
+        <v>36.3382148742676</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>6116</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Requínoa</t>
+        </is>
+      </c>
+      <c r="C129">
+        <v>36.2689476013184</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>6301</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>San Fernando</t>
+        </is>
+      </c>
+      <c r="C130">
+        <v>36.2231521606445</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>6105</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Doñihue</t>
+        </is>
+      </c>
+      <c r="C131">
+        <v>36.1894378662109</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>6201</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Pichilemu</t>
+        </is>
+      </c>
+      <c r="C132">
+        <v>35.9483337402344</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>6206</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Paredones</t>
+        </is>
+      </c>
+      <c r="C133">
+        <v>35.6803970336914</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>6206</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Paredones</t>
+        </is>
+      </c>
+      <c r="C134">
+        <v>35.639778137207</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>6111</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Olivar</t>
+        </is>
+      </c>
+      <c r="C135">
+        <v>35.5883827209473</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>6301</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>San Fernando</t>
+        </is>
+      </c>
+      <c r="C136">
+        <v>35.5155792236328</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>6302</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Chépica</t>
+        </is>
+      </c>
+      <c r="C137">
+        <v>35.4874534606934</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>6114</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Quinta de Tilcoco</t>
+        </is>
+      </c>
+      <c r="C138">
+        <v>35.2351837158203</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>6305</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Nancagua</t>
+        </is>
+      </c>
+      <c r="C139">
+        <v>34.8591537475586</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>6114</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Quinta de Tilcoco</t>
+        </is>
+      </c>
+      <c r="C140">
+        <v>34.7901344299316</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>6307</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Peralillo</t>
+        </is>
+      </c>
+      <c r="C141">
+        <v>34.6061973571777</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>6302</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Chépica</t>
+        </is>
+      </c>
+      <c r="C142">
+        <v>34.4812889099121</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>6310</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Santa Cruz</t>
+        </is>
+      </c>
+      <c r="C143">
+        <v>34.3393058776855</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>6106</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Graneros</t>
+        </is>
+      </c>
+      <c r="C144">
+        <v>34.3360900878906</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>6101</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Rancagua</t>
+        </is>
+      </c>
+      <c r="C145">
+        <v>33.8742523193359</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>6117</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>San Vicente</t>
+        </is>
+      </c>
+      <c r="C146">
+        <v>33.624641418457</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>6108</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Machalí</t>
+        </is>
+      </c>
+      <c r="C147">
+        <v>33.5710029602051</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>6115</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Rengo</t>
+        </is>
+      </c>
+      <c r="C148">
+        <v>33.275951385498</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>6309</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Pumanque</t>
+        </is>
+      </c>
+      <c r="C149">
+        <v>33.1422004699707</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>6206</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Paredones</t>
+        </is>
+      </c>
+      <c r="C150">
+        <v>33.059440612793</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>6304</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Lolol</t>
+        </is>
+      </c>
+      <c r="C151">
+        <v>32.9157371520996</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>6102</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Codegua</t>
+        </is>
+      </c>
+      <c r="C152">
+        <v>32.881233215332</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>6310</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Santa Cruz</t>
+        </is>
+      </c>
+      <c r="C153">
+        <v>32.7697067260742</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>6112</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Peumo</t>
+        </is>
+      </c>
+      <c r="C154">
+        <v>32.7625389099121</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>6103</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Coinco</t>
+        </is>
+      </c>
+      <c r="C155">
+        <v>32.2751312255859</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>6205</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Navidad</t>
+        </is>
+      </c>
+      <c r="C156">
+        <v>32.166805267334</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>6304</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Lolol</t>
+        </is>
+      </c>
+      <c r="C157">
+        <v>32.066520690918</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>6203</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Litueche</t>
+        </is>
+      </c>
+      <c r="C158">
+        <v>31.9640998840332</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>6202</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>La Estrella</t>
+        </is>
+      </c>
+      <c r="C159">
+        <v>31.7925586700439</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>6201</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Pichilemu</t>
+        </is>
+      </c>
+      <c r="C160">
+        <v>31.6741790771484</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>6203</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Litueche</t>
+        </is>
+      </c>
+      <c r="C161">
+        <v>31.5288715362549</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>6309</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Pumanque</t>
+        </is>
+      </c>
+      <c r="C162">
+        <v>31.4295253753662</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>6117</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>San Vicente</t>
+        </is>
+      </c>
+      <c r="C163">
+        <v>31.4217662811279</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>6104</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Coltauco</t>
+        </is>
+      </c>
+      <c r="C164">
+        <v>31.2851505279541</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>6306</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Palmilla</t>
+        </is>
+      </c>
+      <c r="C165">
+        <v>31.1376934051514</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>6107</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Las Cabras</t>
+        </is>
+      </c>
+      <c r="C166">
+        <v>31.0789756774902</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>6303</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Chimbarongo</t>
+        </is>
+      </c>
+      <c r="C167">
+        <v>31.0546226501465</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>6202</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>La Estrella</t>
+        </is>
+      </c>
+      <c r="C168">
+        <v>30.8636856079102</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>6105</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Doñihue</t>
+        </is>
+      </c>
+      <c r="C169">
+        <v>30.8390979766846</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>6111</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Olivar</t>
+        </is>
+      </c>
+      <c r="C170">
+        <v>30.7464141845703</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>6305</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Nancagua</t>
+        </is>
+      </c>
+      <c r="C171">
+        <v>30.2235984802246</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>6110</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Mostazal</t>
+        </is>
+      </c>
+      <c r="C172">
+        <v>30.1923141479492</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>6114</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Quinta de Tilcoco</t>
+        </is>
+      </c>
+      <c r="C173">
+        <v>30.0109786987305</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>6308</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Placilla</t>
+        </is>
+      </c>
+      <c r="C174">
+        <v>29.8105354309082</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>6108</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Machalí</t>
+        </is>
+      </c>
+      <c r="C175">
+        <v>29.5534591674805</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>6103</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Coinco</t>
+        </is>
+      </c>
+      <c r="C176">
+        <v>29.4965934753418</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>6109</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Malloa</t>
+        </is>
+      </c>
+      <c r="C177">
+        <v>29.3389282226562</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>6307</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Peralillo</t>
+        </is>
+      </c>
+      <c r="C178">
+        <v>28.8855419158936</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>6206</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Paredones</t>
+        </is>
+      </c>
+      <c r="C179">
+        <v>28.4197483062744</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>6201</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Pichilemu</t>
+        </is>
+      </c>
+      <c r="C180">
+        <v>28.1783123016357</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>6205</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Navidad</t>
+        </is>
+      </c>
+      <c r="C181">
+        <v>28.145227432251</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>6113</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Pichidegua</t>
+        </is>
+      </c>
+      <c r="C182">
+        <v>27.9123840332031</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>6302</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Chépica</t>
+        </is>
+      </c>
+      <c r="C183">
+        <v>27.4977035522461</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>6201</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Pichilemu</t>
+        </is>
+      </c>
+      <c r="C184">
+        <v>27.1885948181152</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>6205</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Navidad</t>
+        </is>
+      </c>
+      <c r="C185">
+        <v>26.7401027679443</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>6203</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Litueche</t>
+        </is>
+      </c>
+      <c r="C186">
+        <v>24.4643707275391</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>6205</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Navidad</t>
+        </is>
+      </c>
+      <c r="C187">
         <v>24.2151565551758</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>6103</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Coinco</t>
+        </is>
+      </c>
+      <c r="C188">
+        <v>23.9109077453613</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>6304</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Lolol</t>
+        </is>
+      </c>
+      <c r="C189">
+        <v>23.5072917938232</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>6309</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Pumanque</t>
+        </is>
+      </c>
+      <c r="C190">
+        <v>22.4224548339844</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>6202</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>La Estrella</t>
+        </is>
+      </c>
+      <c r="C191">
+        <v>21.6200466156006</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>6205</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Navidad</t>
+        </is>
+      </c>
+      <c r="C192">
+        <v>20.380256652832</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>6206</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Paredones</t>
+        </is>
+      </c>
+      <c r="C193">
+        <v>20.2657909393311</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>6116</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Requínoa</t>
+        </is>
+      </c>
+      <c r="C194">
+        <v>16.6738815307617</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>6102</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Codegua</t>
+        </is>
+      </c>
+      <c r="C195">
+        <v>16.1301422119141</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>6108</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Machalí</t>
+        </is>
+      </c>
+      <c r="C196">
+        <v>14.2006196975708</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>6111</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Olivar</t>
+        </is>
+      </c>
+      <c r="C197">
+        <v>14.0423946380615</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>6106</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Graneros</t>
+        </is>
+      </c>
+      <c r="C198">
+        <v>13.7808752059937</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>6110</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Mostazal</t>
+        </is>
+      </c>
+      <c r="C199">
+        <v>13.4255142211914</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>6112</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Peumo</t>
+        </is>
+      </c>
+      <c r="C200">
+        <v>13.1168003082275</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>6105</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Doñihue</t>
+        </is>
+      </c>
+      <c r="C201">
+        <v>12.4968023300171</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>6115</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Rengo</t>
+        </is>
+      </c>
+      <c r="C202">
+        <v>12.2989158630371</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>6303</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Chimbarongo</t>
+        </is>
+      </c>
+      <c r="C203">
+        <v>12.1221323013306</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>6104</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Coltauco</t>
+        </is>
+      </c>
+      <c r="C204">
+        <v>11.8569459915161</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>6101</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Rancagua</t>
+        </is>
+      </c>
+      <c r="C205">
+        <v>11.7082405090332</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>6301</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>San Fernando</t>
+        </is>
+      </c>
+      <c r="C206">
+        <v>11.4482889175415</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>6107</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Las Cabras</t>
+        </is>
+      </c>
+      <c r="C207">
+        <v>11.3785371780396</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>6306</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Palmilla</t>
+        </is>
+      </c>
+      <c r="C208">
+        <v>11.1907730102539</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>6305</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Nancagua</t>
+        </is>
+      </c>
+      <c r="C209">
+        <v>11.1347513198853</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>6308</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Placilla</t>
+        </is>
+      </c>
+      <c r="C210">
+        <v>10.8822422027588</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>6109</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Malloa</t>
+        </is>
+      </c>
+      <c r="C211">
+        <v>10.5508623123169</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>6113</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Pichidegua</t>
+        </is>
+      </c>
+      <c r="C212">
+        <v>10.4120721817017</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>6307</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Peralillo</t>
+        </is>
+      </c>
+      <c r="C213">
+        <v>9.88021945953369</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>6114</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Quinta de Tilcoco</t>
+        </is>
+      </c>
+      <c r="C214">
+        <v>9.868667602539061</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>6117</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>San Vicente</t>
+        </is>
+      </c>
+      <c r="C215">
+        <v>9.54269599914551</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>6310</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Santa Cruz</t>
+        </is>
+      </c>
+      <c r="C216">
+        <v>9.46584892272949</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>6203</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Litueche</t>
+        </is>
+      </c>
+      <c r="C217">
+        <v>9.2032356262207</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>6103</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Coinco</t>
+        </is>
+      </c>
+      <c r="C218">
+        <v>9.134212493896481</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>6302</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Chépica</t>
+        </is>
+      </c>
+      <c r="C219">
+        <v>8.67708683013916</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>6309</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Pumanque</t>
+        </is>
+      </c>
+      <c r="C220">
+        <v>8.64648532867432</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>6201</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Pichilemu</t>
+        </is>
+      </c>
+      <c r="C221">
+        <v>8.191770553588871</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>6202</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>La Estrella</t>
+        </is>
+      </c>
+      <c r="C222">
+        <v>7.91245794296265</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>6304</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Lolol</t>
+        </is>
+      </c>
+      <c r="C223">
+        <v>7.68598461151123</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>6206</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Paredones</t>
+        </is>
+      </c>
+      <c r="C224">
+        <v>7.03770923614502</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>6205</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Navidad</t>
+        </is>
+      </c>
+      <c r="C225">
+        <v>4.4325213432312</v>
       </c>
     </row>
   </sheetData>
